--- a/漢字（かんじ）/g.xlsx
+++ b/漢字（かんじ）/g.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="1"/>
+    <workbookView windowWidth="23040" windowHeight="9180"/>
   </bookViews>
   <sheets>
     <sheet name="が" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="171">
   <si>
     <t>仮名</t>
   </si>
@@ -168,6 +168,12 @@
   </si>
   <si>
     <t>花柄｜はながら</t>
+  </si>
+  <si>
+    <t>溶</t>
+  </si>
+  <si>
+    <t>溶岩｜ようがん</t>
   </si>
   <si>
     <t>玩</t>
@@ -755,7 +761,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -780,13 +786,6 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1243,148 +1242,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1723,7 +1722,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="20.7777777777778" customWidth="1"/>
@@ -1872,9 +1871,12 @@
       <c r="B8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>31</v>
       </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
     </row>
     <row r="9" ht="18" spans="1:7">
       <c r="A9" s="1" t="s">
@@ -1887,42 +1889,42 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" ht="126" spans="1:7">
+    <row r="10" ht="18" spans="1:7">
       <c r="A10" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="2" t="s">
+    </row>
+    <row r="11" ht="126" spans="1:7">
+      <c r="A11" s="1" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="11" ht="18" spans="1:7">
-      <c r="A11" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" ht="36" spans="1:7">
+    <row r="12" ht="18" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="13" ht="72" spans="1:7">
+    <row r="13" ht="36" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>41</v>
@@ -1931,20 +1933,20 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" ht="18" spans="1:7">
+    <row r="14" ht="72" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:7">
       <c r="A15" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>45</v>
@@ -1955,24 +1957,35 @@
     </row>
     <row r="16" ht="18" spans="1:7">
       <c r="A16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C16" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:3">
       <c r="A17" s="1" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>51</v>
+      </c>
+    </row>
+    <row r="18" ht="18" spans="1:3">
+      <c r="A18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -2003,134 +2016,134 @@
     </row>
     <row r="2" ht="54" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" ht="36" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" ht="36" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" ht="72" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" ht="36" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" ht="22.2" customHeight="1" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" ht="27.6" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:3">
       <c r="A10" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" ht="162" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" ht="72" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" ht="46.8" spans="1:3">
       <c r="A13" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -2161,57 +2174,57 @@
     </row>
     <row r="2" ht="108" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" ht="27.6" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" ht="36" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" ht="73.2" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -2252,181 +2265,181 @@
     </row>
     <row r="2" ht="90" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" ht="72" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="90" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" ht="108" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" ht="36" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:7">
       <c r="A7" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" ht="36" spans="1:7">
       <c r="A8" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" ht="55.8" customHeight="1" spans="1:7">
       <c r="A9" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" ht="72" spans="1:7">
       <c r="A10" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:7">
       <c r="A11" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:7">
       <c r="A12" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" ht="53.4" customHeight="1" spans="1:7">
       <c r="A13" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:7">
       <c r="A14" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" ht="53.4" customHeight="1"/>
@@ -2462,167 +2475,167 @@
     </row>
     <row r="2" ht="18" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" ht="52.2" customHeight="1" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" ht="36" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" ht="72" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" ht="52.8" customHeight="1" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" ht="52.8" customHeight="1" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" ht="18.6" customHeight="1" spans="1:3">
       <c r="A8" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" ht="18.6" customHeight="1" spans="1:3">
       <c r="A9" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" ht="18.6" customHeight="1" spans="1:3">
       <c r="A10" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" ht="159.6" customHeight="1" spans="1:3">
       <c r="A11" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:3">
       <c r="A12" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" ht="27.6" spans="1:3">
       <c r="A13" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:3">
       <c r="A14" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" ht="36" spans="1:3">
       <c r="A15" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" ht="36" spans="1:3">
       <c r="A16" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/漢字（かんじ）/g.xlsx
+++ b/漢字（かんじ）/g.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180"/>
+    <workbookView windowWidth="23040" windowHeight="9180" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="が" sheetId="1" r:id="rId1"/>
@@ -167,7 +167,8 @@
     <t>柄</t>
   </si>
   <si>
-    <t>花柄｜はながら</t>
+    <t>花柄｜はながら
+事柄｜ことがら</t>
   </si>
   <si>
     <t>溶</t>
@@ -426,22 +427,13 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="等线"/>
-        <charset val="134"/>
+        <charset val="128"/>
         <scheme val="minor"/>
       </rPr>
       <t>出口｜でぐち
-蛇口｜じゃぐち</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="等线"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
+蛇口｜じゃぐち
 裏口｜うらぐち
+傷口｜きずぐち
 改札口｜かいさつぐち</t>
     </r>
   </si>
@@ -477,7 +469,8 @@
   </si>
   <si>
     <t>芸術｜げいじゅつ
-工芸品｜こうげいひん</t>
+工芸品｜こうげいひん
+園芸｜えんげい</t>
   </si>
   <si>
     <t>劇</t>
@@ -1397,10 +1390,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1765,7 +1758,7 @@
       <c r="F2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="6" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1847,7 +1840,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" ht="18" spans="1:7">
+    <row r="7" ht="36" spans="1:7">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
@@ -1860,7 +1853,7 @@
       <c r="F7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="2" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2142,7 +2135,7 @@
       <c r="B13" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="5" t="s">
         <v>83</v>
       </c>
     </row>
@@ -2216,14 +2209,14 @@
         <v>94</v>
       </c>
     </row>
-    <row r="6" ht="73.2" spans="1:3">
+    <row r="6" ht="87" spans="1:3">
       <c r="A6" s="1" t="s">
         <v>95</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="2" t="s">
         <v>97</v>
       </c>
     </row>

--- a/漢字（かんじ）/g.xlsx
+++ b/漢字（かんじ）/g.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="3"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="が" sheetId="1" r:id="rId1"/>
@@ -694,7 +694,8 @@
     <t>合</t>
   </si>
   <si>
-    <t>合理的｜ごうりでき
+    <t>混合｜こんごう
+合理的｜ごうりでき
 合格｜ごうかく
 合計｜ごうけい
 集合｜しゅうごう

--- a/漢字（かんじ）/g.xlsx
+++ b/漢字（かんじ）/g.xlsx
@@ -688,7 +688,8 @@
     <t>強</t>
   </si>
   <si>
-    <t>強盗｜ごうとう</t>
+    <t>強盗｜ごうとう
+強情｜ごうじょう</t>
   </si>
   <si>
     <t>合</t>
